--- a/docs/03_test/部門更新のテストケース.xlsx
+++ b/docs/03_test/部門更新のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A13E4D4-806C-49F2-9E54-402476BE1740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB847C6-32A6-4150-9D75-105758C6A5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2E0ED80D-AE7A-4549-B4BA-44C6005F7982}"/>
   </bookViews>
@@ -41,13 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
-    <t>部門登録単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
     <rPh sb="0" eb="2">
       <t>モクジ</t>
@@ -514,6 +507,16 @@
     </rPh>
     <rPh sb="19" eb="20">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門更新単体UIテスト 須崎千穂子</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -586,20 +589,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -713,50 +716,6 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>25384</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>692727</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A6FF52-4C19-AD2E-C43B-B2B1DD7F4D14}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4953000" y="4779818"/>
-          <a:ext cx="2172839" cy="692727"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -780,7 +739,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -824,7 +783,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -868,7 +827,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -912,7 +871,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -956,7 +915,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1000,7 +959,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1044,7 +1003,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1088,7 +1047,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1132,7 +1091,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1176,7 +1135,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1185,6 +1144,50 @@
         <a:xfrm>
           <a:off x="4984750" y="19367501"/>
           <a:ext cx="2300838" cy="1047750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2103548</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>717177</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E00772C5-5507-56D1-70D7-FC8F106F7642}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4960471" y="4788647"/>
+          <a:ext cx="2103548" cy="717177"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1496,284 +1499,284 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="28.25" style="5" customWidth="1"/>
+    <col min="2" max="3" width="28.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="28.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="A1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>16</v>
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>17</v>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>5</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="5" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="95.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="95.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>2</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="5" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:4" ht="113" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="113" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>2</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" spans="1:4" ht="141.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>2</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="A26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" spans="1:4" ht="129.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="119.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>2</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>25</v>
+      <c r="B28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>

--- a/docs/03_test/部門更新のテストケース.xlsx
+++ b/docs/03_test/部門更新のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB847C6-32A6-4150-9D75-105758C6A5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C848987-FE25-4EE3-B2AF-8491536D87C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2E0ED80D-AE7A-4549-B4BA-44C6005F7982}"/>
   </bookViews>
@@ -140,25 +140,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>⑥ホーム画面の部門一覧から新規登録に遷移</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="17">
-      <t>シンキトウロク</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>①正常系を用いて一通り登録できる流れのチェック</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -187,32 +168,6 @@
     <t>テスト結果</t>
     <rPh sb="3" eb="5">
       <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面上部の部門登録ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門登録(入力)画面に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -360,54 +315,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の部門一覧ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門id 1 総務部の更新ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ソウムブ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>更新入力画面に遷移する</t>
     <rPh sb="0" eb="2">
       <t>コウシン</t>
@@ -453,45 +360,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門一覧に戻る画面を押す</t>
-    <rPh sb="0" eb="4">
-      <t>ブモンイチラン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>部門一覧画面に遷移する</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>②部門名の入力必須エラーが正しく出るかチェック</t>
-    <rPh sb="1" eb="3">
-      <t>ブモン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部署名「営業部」と入力して完了ボタンを押す</t>
     <rPh sb="0" eb="3">
       <t>ブショメイ</t>
@@ -511,12 +379,117 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門更新単体UIテスト 須崎千穂子</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
+    <t>部署更新単体UIテスト 須崎千穂子</t>
     <rPh sb="2" eb="4">
       <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑥ホーム画面の部署一覧から新規登録に遷移</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>シンキトウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の部署一覧ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署id 1 総務部の更新ボタンを押す</t>
+    <rPh sb="7" eb="10">
+      <t>ソウムブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧に戻る画面を押す</t>
+    <rPh sb="5" eb="6">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署一覧画面に遷移する</t>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②部署名の入力必須エラーが正しく出るかチェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の部署登録ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部署登録(入力)画面に遷移する</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -598,10 +571,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -627,22 +600,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1950904</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1941</xdr:rowOff>
+      <xdr:colOff>2079625</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>640138</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8921FC2C-35BF-F2B5-22C8-CAC26F959518}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC3C4F74-A822-21C9-3D5C-48F8C87E4C51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -658,8 +631,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4957591" y="2524700"/>
-          <a:ext cx="1950903" cy="1126578"/>
+          <a:off x="4984750" y="2444750"/>
+          <a:ext cx="2079625" cy="640138"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -671,22 +644,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2078183</xdr:colOff>
+      <xdr:colOff>2063750</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>669527</xdr:rowOff>
+      <xdr:rowOff>346494</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E00F883-0C49-F7F0-E483-A65217C2E756}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4317FCD3-1DDC-E185-B673-F67A16E43A5B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -702,8 +675,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953001" y="3659910"/>
-          <a:ext cx="2078182" cy="669526"/>
+          <a:off x="4984750" y="3571876"/>
+          <a:ext cx="2063750" cy="346493"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -716,21 +689,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>166013</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>946728</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2047875</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>322729</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77EC5460-CBE1-7463-88C0-FEC05AB18B7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EA1192B-EA68-FE57-575B-CE257A68238E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -746,8 +719,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953000" y="5899727"/>
-          <a:ext cx="2313468" cy="946728"/>
+          <a:off x="4984750" y="4699001"/>
+          <a:ext cx="2047875" cy="322728"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -760,21 +733,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1962727</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1116557</xdr:rowOff>
+      <xdr:colOff>2127569</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>444501</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DCA592C-524E-F26A-4AF9-E02C21DBE6B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{427EE5A8-B14B-A1E2-4DFC-8CF7E1A07D52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -790,8 +763,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953000" y="7019637"/>
-          <a:ext cx="1962727" cy="1116556"/>
+          <a:off x="4984750" y="5826126"/>
+          <a:ext cx="2127569" cy="444500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -803,22 +776,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>23090</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>80818</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>206872</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>808182</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2032000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>620442</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DB952AE-1FD6-E6F0-65F6-4D2630384D4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663386BC-3DC0-EC8A-75E4-C93FEA973AD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -834,8 +807,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4976090" y="8451273"/>
-          <a:ext cx="2331237" cy="727364"/>
+          <a:off x="4984750" y="6953250"/>
+          <a:ext cx="2032000" cy="620442"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -848,153 +821,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>183782</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>727364</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2111375</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>368353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA3C8711-C01B-4E8B-8E94-49437749E906}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4953000" y="11025909"/>
-          <a:ext cx="2331237" cy="727364"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>183782</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>727364</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{282395F1-6C95-49A4-976B-CE11A2F98699}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4953000" y="14120091"/>
-          <a:ext cx="2331237" cy="727364"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>183782</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>727364</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="図 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0FE9F89-30BA-4497-A8D1-44F64207DF07}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4953000" y="17826182"/>
-          <a:ext cx="2331237" cy="727364"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2112818</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>717640</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8756D97-A63D-C158-7656-A6689EF79E3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6833967-5210-2DB0-0C61-D2C4DEB91C57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1010,8 +851,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953000" y="9582727"/>
-          <a:ext cx="2112818" cy="717640"/>
+          <a:off x="4984750" y="8302625"/>
+          <a:ext cx="2111375" cy="368353"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1024,21 +865,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2101273</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>610979</xdr:rowOff>
+      <xdr:colOff>2047875</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>376337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8189DF8-8020-145E-52B1-CCA587EECE3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EC56016-D3E6-0C4D-7948-77EAE050090C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1054,8 +895,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953000" y="12457545"/>
-          <a:ext cx="2101273" cy="610979"/>
+          <a:off x="4984750" y="9509125"/>
+          <a:ext cx="2047875" cy="376337"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1068,21 +909,65 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2147419</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>842818</xdr:rowOff>
+      <xdr:colOff>2111375</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>368353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="図 29">
+        <xdr:cNvPr id="11" name="図 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7108B8DA-ACF8-A360-4986-799D2A64CA25}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9532598B-2921-4FCE-976A-913A5776361A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4984750" y="10937875"/>
+          <a:ext cx="2111375" cy="368353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>341075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9B947EA-2994-99B0-A6B0-7524051A6215}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1098,8 +983,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4953000" y="15921182"/>
-          <a:ext cx="2147419" cy="842818"/>
+          <a:off x="4984750" y="12366626"/>
+          <a:ext cx="2159000" cy="341074"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1111,22 +996,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>141838</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>1047751</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1952625</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>507044</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="図 31">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20B82AB-9576-27A9-EE88-17D625A3A72D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB910D67-8971-E350-44CE-13D3FBAAABD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1142,8 +1027,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4984750" y="19367501"/>
-          <a:ext cx="2300838" cy="1047750"/>
+          <a:off x="4984751" y="15811501"/>
+          <a:ext cx="1952624" cy="507043"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1156,21 +1041,109 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2103548</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>717177</xdr:rowOff>
+      <xdr:colOff>2111375</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>368353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="14" name="図 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E00772C5-5507-56D1-70D7-FC8F106F7642}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32227687-EB56-45A9-A079-E8FF9B48F52B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4984750" y="14017625"/>
+          <a:ext cx="2111375" cy="368353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2111375</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>368353</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A340EEA9-1164-4B62-A359-E28E04C0DBB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4984750" y="17716500"/>
+          <a:ext cx="2111375" cy="368353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>213970</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>492125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FFDF8A1-9E46-F869-69F5-771495AD595A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1186,8 +1159,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4960471" y="4788647"/>
-          <a:ext cx="2103548" cy="717177"/>
+          <a:off x="4984750" y="19367500"/>
+          <a:ext cx="2372970" cy="492125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1504,12 +1477,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
@@ -1561,7 +1534,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1573,25 +1546,25 @@
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1599,10 +1572,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1610,10 +1583,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1621,10 +1594,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1632,10 +1605,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1650,22 +1623,22 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" ht="95.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="95.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1673,29 +1646,29 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="A20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:4" ht="113" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="113" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1703,29 +1676,29 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="A23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:4" ht="141.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="132" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1733,29 +1706,29 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:4" ht="129.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="119.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1763,20 +1736,20 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A26:D26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
